--- a/lab3/Циклы.xlsx
+++ b/lab3/Циклы.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
   <si>
     <t>Команда</t>
   </si>
@@ -95,11 +95,6 @@
     <t>Dxxx</t>
   </si>
   <si>
-    <t>DR -&gt; BR
-IP -&gt; DR
-BR -&gt; IP</t>
-  </si>
-  <si>
     <t>Exxx</t>
   </si>
   <si>
@@ -220,6 +215,81 @@
   <si>
     <t>~DT AND ~AC -&gt; BR
 ~BR -&gt; AC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR -&gt; BR
+IP -&gt; DR
+BR -&gt; IP
+~0 + SP -&gt; SP, AR
+DR -&gt; MEM(AR)
+</t>
+  </si>
+  <si>
+    <t>0800</t>
+  </si>
+  <si>
+    <t>SP -&gt; AR
+MEM(AR) -&gt; DR
+DR -&gt; AC, NZV
+SP + 1 -&gt; SP</t>
+  </si>
+  <si>
+    <t>0900</t>
+  </si>
+  <si>
+    <t>SP -&gt; AR
+MEM(AR) -&gt; DR
+DR -&gt; PS
+DR -&gt; AC, NZV
+SP + 1 -&gt; SP</t>
+  </si>
+  <si>
+    <t>0A00</t>
+  </si>
+  <si>
+    <t>0B00</t>
+  </si>
+  <si>
+    <t>SP -&gt; AR
+MEM(AR) -&gt; DR
+DR -&gt; IP
+SP + 1 -&gt; SP</t>
+  </si>
+  <si>
+    <t>SP -&gt; AR
+MEM(AR) -&gt; DR
+DR -&gt; PS
+SP + 1 -&gt; SP, AR
+MEM(AR) -&gt; DR
+DR -&gt; IP
+SP + 1 -&gt; SP</t>
+  </si>
+  <si>
+    <t>0C00</t>
+  </si>
+  <si>
+    <t>AC -&gt; DR
+~0 + SP -&gt; SP, AR
+DR -&gt; MEM(AR)</t>
+  </si>
+  <si>
+    <t>0D00</t>
+  </si>
+  <si>
+    <t>PS -&gt; DR
+~0 + SP -&gt; SP, AR
+DR -&gt; MEM(AR)</t>
+  </si>
+  <si>
+    <t>0E00</t>
+  </si>
+  <si>
+    <t>SP -&gt; AR
+MEM(AR) -DR
+DR -&gt; BR
+AC -&gt; DR
+BR -&gt; AC, N, Z, V, C;
+DR -&gt; MEM(AR)</t>
   </si>
 </sst>
 </file>
@@ -270,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -302,6 +372,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -582,16 +659,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="26.140625" customWidth="1"/>
     <col min="4" max="4" width="34.42578125" customWidth="1"/>
     <col min="5" max="5" width="30.28515625" customWidth="1"/>
+    <col min="12" max="12" width="8.28515625" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="17" max="17" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -608,7 +690,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -620,8 +702,19 @@
       <c r="E2" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="str">
         <f>LEFT(A2,1)+1 &amp; "xxx"</f>
         <v>3xxx</v>
@@ -632,10 +725,19 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="str">
         <f t="shared" ref="A4:A8" si="0">LEFT(A3,1)+1 &amp; "xxx"</f>
         <v>4xxx</v>
@@ -648,8 +750,17 @@
       <c r="E4" s="8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L4" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="P4" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="str">
         <f t="shared" si="0"/>
         <v>5xxx</v>
@@ -660,10 +771,19 @@
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="P5" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="187.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="str">
         <f t="shared" si="0"/>
         <v>6xxx</v>
@@ -676,8 +796,17 @@
       <c r="E6" s="10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L6" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="P6" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <f>LEFT(A6,1)+1 &amp; "xxx"</f>
         <v>7xxx</v>
@@ -688,10 +817,19 @@
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="P7" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <f t="shared" si="0"/>
         <v>8xxx</v>
@@ -702,10 +840,16 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="P8" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -717,8 +861,14 @@
       <c r="E9" s="10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L9" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="P9" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
@@ -731,7 +881,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
@@ -744,7 +894,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>18</v>
       </c>
@@ -754,12 +904,12 @@
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>14</v>
@@ -767,12 +917,12 @@
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>14</v>
@@ -780,84 +930,84 @@
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
       <c r="E15" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
       <c r="E16" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
       <c r="E17" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
       <c r="E18" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
       <c r="E19" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
       <c r="E20" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
       <c r="E21" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -866,10 +1016,10 @@
         <v>101</v>
       </c>
       <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" t="s">
         <v>39</v>
-      </c>
-      <c r="D34" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -877,7 +1027,7 @@
         <v>102</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -885,7 +1035,7 @@
         <v>103</v>
       </c>
       <c r="D36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -899,7 +1049,7 @@
         <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -910,7 +1060,7 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -937,7 +1087,7 @@
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -945,7 +1095,7 @@
         <v>109</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">

--- a/lab3/Циклы.xlsx
+++ b/lab3/Циклы.xlsx
@@ -1,23 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\OPD\lab3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\Opd\lab3\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F787A3-3B17-401D-8348-4D9E46843ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12135"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -295,7 +305,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -340,39 +350,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -658,22 +657,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" customWidth="1"/>
-    <col min="4" max="4" width="34.42578125" customWidth="1"/>
-    <col min="5" max="5" width="30.28515625" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" customWidth="1"/>
+    <col min="3" max="3" width="26.1796875" customWidth="1"/>
+    <col min="4" max="4" width="34.453125" customWidth="1"/>
+    <col min="5" max="5" width="30.26953125" customWidth="1"/>
+    <col min="12" max="12" width="8.26953125" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
     <col min="14" max="15" width="15" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
     <col min="17" max="17" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,31 +689,31 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="11" t="s">
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="str">
         <f>LEFT(A2,1)+1 &amp; "xxx"</f>
         <v>3xxx</v>
@@ -722,22 +721,22 @@
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="str">
         <f t="shared" ref="A4:A8" si="0">LEFT(A3,1)+1 &amp; "xxx"</f>
         <v>4xxx</v>
@@ -745,22 +744,22 @@
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="L4" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="P4" s="10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="str">
         <f t="shared" si="0"/>
         <v>5xxx</v>
@@ -768,22 +767,22 @@
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="15" t="s">
+      <c r="P5" s="10" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="187.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="187.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="str">
         <f t="shared" si="0"/>
         <v>6xxx</v>
@@ -791,22 +790,22 @@
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="10" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P6" s="15" t="s">
+      <c r="P6" s="10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="str">
         <f>LEFT(A6,1)+1 &amp; "xxx"</f>
         <v>7xxx</v>
@@ -814,22 +813,22 @@
       <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="10" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="15" t="s">
+      <c r="M7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P7" s="15" t="s">
+      <c r="P7" s="10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="str">
         <f t="shared" si="0"/>
         <v>8xxx</v>
@@ -837,181 +836,181 @@
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="P8" s="15" t="s">
+      <c r="P8" s="10" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="96.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="10" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="P9" s="15" t="s">
+      <c r="P9" s="10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="10" t="s">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="11" t="s">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="11" t="s">
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="11" t="s">
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="11" t="s">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:16" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="11" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="11" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="11" t="s">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="11" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="11" t="s">
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="11" t="s">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>101</v>
       </c>
@@ -1022,7 +1021,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>102</v>
       </c>
@@ -1030,7 +1029,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>103</v>
       </c>
@@ -1038,7 +1037,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>104</v>
       </c>
@@ -1052,7 +1051,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>105</v>
       </c>
@@ -1063,7 +1062,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>106</v>
       </c>
@@ -1071,7 +1070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>107</v>
       </c>
@@ -1079,7 +1078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>108</v>
       </c>
@@ -1090,7 +1089,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>109</v>
       </c>
@@ -1098,17 +1097,17 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>110</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>112</v>
       </c>
